--- a/output-submit/门店分级与调整建议.xlsx
+++ b/output-submit/门店分级与调整建议.xlsx
@@ -3325,16 +3325,16 @@
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation sqref="K2:K43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
+    <dataValidation sqref="K2:K200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
+    <dataValidation sqref="L2:L200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
       <formula1>"A,B,C,D"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
+    <dataValidation sqref="M2:M200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
       <formula1>"维持,整改,转前置仓或自提点,闭店评估"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
+    <dataValidation sqref="O2:O200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
       <formula1>"已确认,待补"</formula1>
     </dataValidation>
   </dataValidations>
